--- a/data/LifeICICISmartPlusTestData.xlsx
+++ b/data/LifeICICISmartPlusTestData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="284">
   <si>
     <t>Execute</t>
   </si>
@@ -29,6 +29,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>PlanName</t>
+  </si>
+  <si>
     <t>CIF</t>
   </si>
   <si>
@@ -95,163 +98,172 @@
     <t>Positive</t>
   </si>
   <si>
+    <t>iProtect Smart Plus</t>
+  </si>
+  <si>
+    <t>Yearly</t>
+  </si>
+  <si>
+    <t>PASS – minimum plan SA, minimum entry age, minimum maturity age, minimum PT; Single supported.</t>
+  </si>
+  <si>
+    <t>TC_02</t>
+  </si>
+  <si>
+    <t>Max Age Maturity</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>PASS – maximum entry age and maturity age; Monthly supported.</t>
+  </si>
+  <si>
+    <t>TC_03</t>
+  </si>
+  <si>
+    <t>Max PT PPT</t>
+  </si>
+  <si>
+    <t>PASS – Annual supported; PPT at plan maximum and PT within plan maximum.</t>
+  </si>
+  <si>
+    <t>TC_04</t>
+  </si>
+  <si>
+    <t>CI Valid Boundary</t>
+  </si>
+  <si>
+    <t>Health Protect Rider (CI)</t>
+  </si>
+  <si>
+    <t>20 CI Package</t>
+  </si>
+  <si>
+    <t>PASS – R73: SI=60% of base SA, 600k multiple of 50k; PT/PPT at R73 max 20; 20 CI package.</t>
+  </si>
+  <si>
+    <t>TC_05</t>
+  </si>
+  <si>
+    <t>CI Max Boundary</t>
+  </si>
+  <si>
+    <t>60 CI Package</t>
+  </si>
+  <si>
+    <t>PASS – R73: base SA at rider slab max, age/maturity/PT/PPT at rider maxima, SI=60%, 60 CI package.</t>
+  </si>
+  <si>
+    <t>TC_06</t>
+  </si>
+  <si>
+    <t>ATPD Min Boundary</t>
+  </si>
+  <si>
+    <t>Half-Yearly</t>
+  </si>
+  <si>
+    <t>Accidental Total &amp; Permanent Disability</t>
+  </si>
+  <si>
+    <t>PASS – R114 minimum rider SA/base SA; minimum age/maturity/PT/PPT; SI=1x base.</t>
+  </si>
+  <si>
+    <t>TC_07</t>
+  </si>
+  <si>
+    <t>ATPD Max Boundary</t>
+  </si>
+  <si>
+    <t>PASS – R114 maximum rider/base SA, age/maturity/PT/PPT maxima; SI=1x base.</t>
+  </si>
+  <si>
+    <t>TC_08</t>
+  </si>
+  <si>
+    <t>WOP Max Boundary</t>
+  </si>
+  <si>
+    <t>Waiver of Premium(WOP)</t>
+  </si>
+  <si>
+    <t>PASS – R76: age/maturity/PT/PPT maxima; SI remains 0.</t>
+  </si>
+  <si>
+    <t>TC_09</t>
+  </si>
+  <si>
+    <t>ADC Max Boundary</t>
+  </si>
+  <si>
+    <t>Accidental Death Cover</t>
+  </si>
+  <si>
+    <t>PASS – R83: SI=3x base SA = 30m, at rider SI max; PT/PPT/age/maturity at maxima.</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t>ADC Min Boundary</t>
+  </si>
+  <si>
+    <t>PASS – R83: SI=3x base SA = 1.5m; minimum base SA/age/maturity/PT/PPT.</t>
+  </si>
+  <si>
+    <t>TC_11</t>
+  </si>
+  <si>
+    <t>ATPD ADC Combination</t>
+  </si>
+  <si>
+    <t>PASS – R114 + R83 combination allowed; each SI follows its own ratio.</t>
+  </si>
+  <si>
+    <t>TC_12</t>
+  </si>
+  <si>
+    <t>CI ATPD Combination</t>
+  </si>
+  <si>
+    <t>PASS – R73 + R114 combination allowed; CI SI=60%, ATPD SI=1x.</t>
+  </si>
+  <si>
+    <t>TC_13</t>
+  </si>
+  <si>
+    <t>CI ADC Combination</t>
+  </si>
+  <si>
+    <t>PASS – R73 + R83 combination allowed; CI SI=60%, ADC SI=3x.</t>
+  </si>
+  <si>
+    <t>TC_14</t>
+  </si>
+  <si>
+    <t>Plan SA Minimum</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>FAIL – plan SA below minimum 50,00,000.</t>
+  </si>
+  <si>
+    <t>SumAssured &lt; plan minimum 50,00,000.</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>TC_15</t>
+  </si>
+  <si>
+    <t>CI SI Ratio</t>
+  </si>
+  <si>
     <t>Single</t>
-  </si>
-  <si>
-    <t>PASS – minimum plan SA, minimum entry age, minimum maturity age, minimum PT; Single supported.</t>
-  </si>
-  <si>
-    <t>TC_02</t>
-  </si>
-  <si>
-    <t>Max Age Maturity</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>PASS – maximum entry age and maturity age; Monthly supported.</t>
-  </si>
-  <si>
-    <t>TC_03</t>
-  </si>
-  <si>
-    <t>Max PT PPT</t>
-  </si>
-  <si>
-    <t>Annual</t>
-  </si>
-  <si>
-    <t>PASS – Annual supported; PPT at plan maximum and PT within plan maximum.</t>
-  </si>
-  <si>
-    <t>TC_04</t>
-  </si>
-  <si>
-    <t>CI Valid Boundary</t>
-  </si>
-  <si>
-    <t>Health Protect Rider (CI)</t>
-  </si>
-  <si>
-    <t>20 CI Package</t>
-  </si>
-  <si>
-    <t>PASS – R73: SI=60% of base SA, 600k multiple of 50k; PT/PPT at R73 max 20; 20 CI package.</t>
-  </si>
-  <si>
-    <t>TC_05</t>
-  </si>
-  <si>
-    <t>CI Max Boundary</t>
-  </si>
-  <si>
-    <t>60 CI Package</t>
-  </si>
-  <si>
-    <t>PASS – R73: base SA at rider slab max, age/maturity/PT/PPT at rider maxima, SI=60%, 60 CI package.</t>
-  </si>
-  <si>
-    <t>TC_06</t>
-  </si>
-  <si>
-    <t>ATPD Min Boundary</t>
-  </si>
-  <si>
-    <t>Accidental Total &amp; Permanent Disability</t>
-  </si>
-  <si>
-    <t>PASS – R114 minimum rider SA/base SA; minimum age/maturity/PT/PPT; SI=1x base.</t>
-  </si>
-  <si>
-    <t>TC_07</t>
-  </si>
-  <si>
-    <t>ATPD Max Boundary</t>
-  </si>
-  <si>
-    <t>PASS – R114 maximum rider/base SA, age/maturity/PT/PPT maxima; SI=1x base.</t>
-  </si>
-  <si>
-    <t>TC_08</t>
-  </si>
-  <si>
-    <t>WOP Max Boundary</t>
-  </si>
-  <si>
-    <t>Waiver of Premium(WOP)</t>
-  </si>
-  <si>
-    <t>PASS – R76: age/maturity/PT/PPT maxima; SI remains 0.</t>
-  </si>
-  <si>
-    <t>TC_09</t>
-  </si>
-  <si>
-    <t>ADC Max Boundary</t>
-  </si>
-  <si>
-    <t>Accidental Death Cover</t>
-  </si>
-  <si>
-    <t>PASS – R83: SI=3x base SA = 30m, at rider SI max; PT/PPT/age/maturity at maxima.</t>
-  </si>
-  <si>
-    <t>TC_10</t>
-  </si>
-  <si>
-    <t>ADC Min Boundary</t>
-  </si>
-  <si>
-    <t>PASS – R83: SI=3x base SA = 1.5m; minimum base SA/age/maturity/PT/PPT.</t>
-  </si>
-  <si>
-    <t>TC_11</t>
-  </si>
-  <si>
-    <t>ATPD ADC Combination</t>
-  </si>
-  <si>
-    <t>PASS – R114 + R83 combination allowed; each SI follows its own ratio.</t>
-  </si>
-  <si>
-    <t>TC_12</t>
-  </si>
-  <si>
-    <t>CI ATPD Combination</t>
-  </si>
-  <si>
-    <t>PASS – R73 + R114 combination allowed; CI SI=60%, ATPD SI=1x.</t>
-  </si>
-  <si>
-    <t>TC_13</t>
-  </si>
-  <si>
-    <t>CI ADC Combination</t>
-  </si>
-  <si>
-    <t>PASS – R73 + R83 combination allowed; CI SI=60%, ADC SI=3x.</t>
-  </si>
-  <si>
-    <t>TC_14</t>
-  </si>
-  <si>
-    <t>Plan SA Minimum</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>FAIL – plan SA below minimum 500,000.</t>
-  </si>
-  <si>
-    <t>SumAssured &lt; plan minimum 500,000.</t>
-  </si>
-  <si>
-    <t>TC_15</t>
-  </si>
-  <si>
-    <t>CI SI Ratio</t>
   </si>
   <si>
     <t>FAIL – plan/rider entry age invalid.</t>
@@ -861,7 +873,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -876,11 +888,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -890,6 +907,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5596"/>
       </patternFill>
     </fill>
     <fill>
@@ -924,17 +946,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1276,28 +1299,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="41" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="41" customWidth="1"/>
-    <col min="16" max="18" width="12" customWidth="1"/>
-    <col min="19" max="19" width="21.428571428571427" customWidth="1"/>
-    <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="22" width="42.142857142857146" customWidth="1"/>
-    <col min="23" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="13.571428571428571" customWidth="1"/>
+    <col min="6" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="41" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="41" customWidth="1"/>
+    <col min="17" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="21.428571428571427" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="23" width="42.142857142857146" customWidth="1"/>
+    <col min="24" max="25" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1335,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1364,1680 +1389,1797 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2">
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
         <v>987991</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>5000000</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>18</v>
       </c>
-      <c r="H2">
-        <v>23</v>
-      </c>
       <c r="I2">
+        <v>23</v>
+      </c>
+      <c r="J2">
         <v>5</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U2" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3">
+      <c r="F3">
         <v>987992</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>10000000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>60</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>85</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
       </c>
       <c r="J3">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="U3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
         <v>987991</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>5000000</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>18</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>85</v>
-      </c>
-      <c r="I4">
-        <v>67</v>
       </c>
       <c r="J4">
         <v>67</v>
       </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="U4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>67</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5">
+        <v>38</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
         <v>987991</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>10000000</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>18</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>38</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
       </c>
       <c r="J5">
         <v>20</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
+      <c r="K5">
+        <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
         <v>39</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5">
         <v>600000</v>
       </c>
-      <c r="U5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6">
+        <v>43</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6">
         <v>15000000</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>55</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>75</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
       </c>
       <c r="J6">
         <v>20</v>
       </c>
-      <c r="K6" t="s">
-        <v>34</v>
+      <c r="K6">
+        <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6">
         <v>9000000</v>
       </c>
-      <c r="U6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7">
+        <v>47</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
         <v>987991</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>5000000</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>18</v>
       </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
       <c r="I7">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" t="s">
-        <v>47</v>
-      </c>
-      <c r="P7">
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q7">
         <v>500000</v>
       </c>
-      <c r="U7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
         <v>987992</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>30000000</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>60</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>85</v>
-      </c>
-      <c r="I8">
-        <v>62</v>
       </c>
       <c r="J8">
         <v>62</v>
       </c>
-      <c r="K8" t="s">
-        <v>34</v>
-      </c>
-      <c r="O8" t="s">
-        <v>47</v>
-      </c>
-      <c r="P8">
+      <c r="K8">
+        <v>62</v>
+      </c>
+      <c r="L8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q8">
         <v>30000000</v>
       </c>
-      <c r="U8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9">
+        <v>55</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9">
         <v>5000000</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>55</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>75</v>
-      </c>
-      <c r="I9">
-        <v>57</v>
       </c>
       <c r="J9">
         <v>57</v>
       </c>
-      <c r="K9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>54</v>
-      </c>
-      <c r="R9">
+      <c r="K9">
+        <v>57</v>
+      </c>
+      <c r="L9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9">
         <v>0</v>
       </c>
-      <c r="U9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
         <v>987992</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>10000000</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>60</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>85</v>
-      </c>
-      <c r="I10">
-        <v>67</v>
       </c>
       <c r="J10">
         <v>67</v>
       </c>
-      <c r="K10" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" t="s">
-        <v>58</v>
-      </c>
-      <c r="T10">
+      <c r="K10">
+        <v>67</v>
+      </c>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T10" t="s">
+        <v>60</v>
+      </c>
+      <c r="U10">
         <v>30000000</v>
       </c>
-      <c r="U10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11">
+        <v>63</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11">
         <v>987991</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>5000000</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>18</v>
       </c>
-      <c r="H11">
-        <v>23</v>
-      </c>
       <c r="I11">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" t="s">
+        <v>60</v>
+      </c>
+      <c r="U11">
+        <v>1500000</v>
+      </c>
+      <c r="V11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12">
+        <v>987990</v>
+      </c>
+      <c r="G12">
+        <v>5000000</v>
+      </c>
+      <c r="H12">
         <v>30</v>
       </c>
-      <c r="S11" t="s">
-        <v>58</v>
-      </c>
-      <c r="T11">
-        <v>1500000</v>
-      </c>
-      <c r="U11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12">
-        <v>987990</v>
-      </c>
-      <c r="F12">
-        <v>5000000</v>
-      </c>
-      <c r="G12">
-        <v>30</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>80</v>
-      </c>
-      <c r="I12">
-        <v>50</v>
       </c>
       <c r="J12">
         <v>50</v>
       </c>
-      <c r="K12" t="s">
-        <v>30</v>
+      <c r="K12">
+        <v>50</v>
       </c>
       <c r="L12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M12" t="s">
         <v>39</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12">
         <v>50000</v>
       </c>
-      <c r="O12" t="s">
-        <v>47</v>
-      </c>
-      <c r="P12">
+      <c r="P12" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q12">
         <v>5000000</v>
       </c>
-      <c r="S12" t="s">
-        <v>58</v>
-      </c>
-      <c r="T12">
+      <c r="T12" t="s">
+        <v>60</v>
+      </c>
+      <c r="U12">
         <v>15000000</v>
       </c>
-      <c r="U12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13">
         <v>987990</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>5000000</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>30</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>80</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>50</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>20</v>
       </c>
-      <c r="K13" t="s">
-        <v>34</v>
-      </c>
       <c r="L13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M13" t="s">
-        <v>43</v>
-      </c>
-      <c r="N13">
+        <v>39</v>
+      </c>
+      <c r="N13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13">
         <v>3000000</v>
       </c>
-      <c r="O13" t="s">
-        <v>47</v>
-      </c>
-      <c r="P13">
+      <c r="P13" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q13">
         <v>5000000</v>
       </c>
-      <c r="U13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14">
         <v>987990</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>5000000</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>30</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>80</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>50</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>20</v>
       </c>
-      <c r="K14" t="s">
-        <v>34</v>
-      </c>
       <c r="L14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M14" t="s">
         <v>39</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="s">
+        <v>40</v>
+      </c>
+      <c r="O14">
         <v>3000000</v>
       </c>
-      <c r="S14" t="s">
-        <v>58</v>
-      </c>
-      <c r="T14">
+      <c r="T14" t="s">
+        <v>60</v>
+      </c>
+      <c r="U14">
         <v>15000000</v>
       </c>
-      <c r="U14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15">
+        <v>987991</v>
+      </c>
+      <c r="G15">
+        <v>4999999</v>
+      </c>
+      <c r="H15">
+        <v>18</v>
+      </c>
+      <c r="I15">
+        <v>23</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15" t="s">
+        <v>28</v>
+      </c>
+      <c r="V15" t="s">
+        <v>77</v>
+      </c>
+      <c r="W15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16">
+        <v>5000000</v>
+      </c>
+      <c r="H16">
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>23</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s">
+        <v>83</v>
+      </c>
+      <c r="W16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17">
+        <v>987991</v>
+      </c>
+      <c r="G17">
+        <v>5000000</v>
+      </c>
+      <c r="H17">
+        <v>18</v>
+      </c>
+      <c r="I17">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15">
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s">
+        <v>87</v>
+      </c>
+      <c r="W17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18">
         <v>987991</v>
       </c>
-      <c r="F15">
-        <v>4999999</v>
-      </c>
-      <c r="G15">
+      <c r="G18">
+        <v>5000000</v>
+      </c>
+      <c r="H18">
         <v>18</v>
       </c>
-      <c r="H15">
-        <v>23</v>
-      </c>
-      <c r="I15">
+      <c r="I18">
+        <v>22</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18" t="s">
+        <v>28</v>
+      </c>
+      <c r="V18" t="s">
+        <v>91</v>
+      </c>
+      <c r="W18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19">
+        <v>987991</v>
+      </c>
+      <c r="G19">
+        <v>5000000</v>
+      </c>
+      <c r="H19">
+        <v>18</v>
+      </c>
+      <c r="I19">
+        <v>23</v>
+      </c>
+      <c r="J19">
         <v>5</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" t="s">
-        <v>75</v>
-      </c>
-      <c r="V15" t="s">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>82</v>
+      </c>
+      <c r="V19" t="s">
+        <v>95</v>
+      </c>
+      <c r="W19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16">
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20">
+        <v>987991</v>
+      </c>
+      <c r="G20">
         <v>5000000</v>
       </c>
-      <c r="G16">
-        <v>17</v>
-      </c>
-      <c r="H16">
-        <v>23</v>
-      </c>
-      <c r="I16">
-        <v>5</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="s">
-        <v>26</v>
-      </c>
-      <c r="U16" t="s">
-        <v>79</v>
-      </c>
-      <c r="V16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17">
-        <v>987991</v>
-      </c>
-      <c r="F17">
-        <v>5000000</v>
-      </c>
-      <c r="G17">
+      <c r="H20">
         <v>18</v>
       </c>
-      <c r="H17">
-        <v>22</v>
-      </c>
-      <c r="I17">
-        <v>5</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
-      <c r="U17" t="s">
-        <v>83</v>
-      </c>
-      <c r="V17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="I20">
         <v>86</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18">
-        <v>987991</v>
-      </c>
-      <c r="F18">
-        <v>5000000</v>
-      </c>
-      <c r="G18">
-        <v>18</v>
-      </c>
-      <c r="H18">
-        <v>23</v>
-      </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="U18" t="s">
-        <v>87</v>
-      </c>
-      <c r="V18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19">
-        <v>987991</v>
-      </c>
-      <c r="F19">
-        <v>5000000</v>
-      </c>
-      <c r="G19">
-        <v>18</v>
-      </c>
-      <c r="H19">
-        <v>23</v>
-      </c>
-      <c r="I19">
-        <v>5</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" t="s">
-        <v>26</v>
-      </c>
-      <c r="U19" t="s">
-        <v>91</v>
-      </c>
-      <c r="V19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20">
-        <v>987991</v>
-      </c>
-      <c r="F20">
-        <v>5000000</v>
-      </c>
-      <c r="G20">
-        <v>18</v>
-      </c>
-      <c r="H20">
-        <v>23</v>
-      </c>
-      <c r="I20">
-        <v>67</v>
       </c>
       <c r="J20">
         <v>68</v>
       </c>
-      <c r="K20" t="s">
-        <v>26</v>
-      </c>
-      <c r="U20" t="s">
-        <v>91</v>
+      <c r="K20">
+        <v>68</v>
+      </c>
+      <c r="L20" t="s">
+        <v>28</v>
       </c>
       <c r="V20" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21">
+        <v>101</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21">
         <v>10000000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>17</v>
       </c>
-      <c r="H21">
-        <v>23</v>
-      </c>
       <c r="I21">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J21">
         <v>5</v>
       </c>
-      <c r="K21" t="s">
-        <v>30</v>
-      </c>
-      <c r="O21" t="s">
-        <v>47</v>
-      </c>
-      <c r="P21">
+      <c r="K21">
+        <v>5</v>
+      </c>
+      <c r="L21" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q21">
         <v>1000000</v>
       </c>
-      <c r="U21" t="s">
-        <v>98</v>
-      </c>
       <c r="V21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="W21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22">
+        <v>105</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22">
         <v>987992</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>10000000</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>60</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>75</v>
-      </c>
-      <c r="I22">
-        <v>20</v>
       </c>
       <c r="J22">
         <v>20</v>
       </c>
-      <c r="K22" t="s">
-        <v>30</v>
+      <c r="K22">
+        <v>20</v>
       </c>
       <c r="L22" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M22" t="s">
         <v>39</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="s">
+        <v>40</v>
+      </c>
+      <c r="O22">
         <v>600000</v>
       </c>
-      <c r="U22" t="s">
-        <v>102</v>
-      </c>
       <c r="V22" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="W22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23">
+        <v>109</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23">
         <v>987991</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>10000000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>18</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>39</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>21</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>20</v>
       </c>
-      <c r="K23" t="s">
-        <v>30</v>
-      </c>
       <c r="L23" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M23" t="s">
         <v>39</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="s">
+        <v>40</v>
+      </c>
+      <c r="O23">
         <v>600000</v>
       </c>
-      <c r="U23" t="s">
-        <v>106</v>
-      </c>
       <c r="V23" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="W23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24">
+        <v>113</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24">
         <v>987991</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>10000000</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>18</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>39</v>
-      </c>
-      <c r="I24">
-        <v>20</v>
       </c>
       <c r="J24">
         <v>21</v>
       </c>
-      <c r="K24" t="s">
-        <v>30</v>
+      <c r="K24">
+        <v>21</v>
       </c>
       <c r="L24" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M24" t="s">
         <v>39</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="s">
+        <v>40</v>
+      </c>
+      <c r="O24">
         <v>600000</v>
       </c>
-      <c r="U24" t="s">
-        <v>110</v>
-      </c>
       <c r="V24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="W24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25">
+        <v>117</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25">
         <v>987991</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>10000000</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>18</v>
       </c>
-      <c r="H25">
-        <v>80</v>
-      </c>
       <c r="I25">
+        <v>81</v>
+      </c>
+      <c r="J25">
         <v>63</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>62</v>
       </c>
-      <c r="K25" t="s">
-        <v>30</v>
-      </c>
-      <c r="O25" t="s">
-        <v>47</v>
-      </c>
-      <c r="P25">
+      <c r="L25" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q25">
         <v>1000000</v>
       </c>
-      <c r="U25" t="s">
-        <v>114</v>
-      </c>
       <c r="V25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="W25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26">
+        <v>121</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26">
         <v>987991</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>10000000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>18</v>
       </c>
-      <c r="H26">
-        <v>75</v>
-      </c>
       <c r="I26">
+        <v>76</v>
+      </c>
+      <c r="J26">
         <v>58</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>57</v>
       </c>
-      <c r="K26" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>54</v>
-      </c>
-      <c r="R26">
+      <c r="L26" t="s">
+        <v>28</v>
+      </c>
+      <c r="R26" t="s">
+        <v>56</v>
+      </c>
+      <c r="S26">
         <v>0</v>
       </c>
-      <c r="U26" t="s">
-        <v>118</v>
-      </c>
       <c r="V26" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="W26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27">
+        <v>125</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27">
         <v>987991</v>
       </c>
-      <c r="F27">
-        <v>10000000</v>
-      </c>
       <c r="G27">
+        <v>5000000</v>
+      </c>
+      <c r="H27">
         <v>18</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>38</v>
-      </c>
-      <c r="I27">
-        <v>20</v>
       </c>
       <c r="J27">
         <v>20</v>
       </c>
-      <c r="K27" t="s">
-        <v>30</v>
+      <c r="K27">
+        <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M27" t="s">
         <v>39</v>
       </c>
-      <c r="N27">
-        <v>500000</v>
-      </c>
-      <c r="U27" t="s">
-        <v>122</v>
+      <c r="N27" t="s">
+        <v>40</v>
+      </c>
+      <c r="O27">
+        <v>6000000</v>
       </c>
       <c r="V27" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="W27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28">
+        <v>129</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28">
         <v>987991</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>10000000</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>18</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>38</v>
-      </c>
-      <c r="I28">
-        <v>20</v>
       </c>
       <c r="J28">
         <v>20</v>
       </c>
-      <c r="K28" t="s">
-        <v>30</v>
+      <c r="K28">
+        <v>20</v>
       </c>
       <c r="L28" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M28" t="s">
         <v>39</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="s">
+        <v>40</v>
+      </c>
+      <c r="O28">
         <v>610000</v>
-      </c>
-      <c r="U28" t="s">
-        <v>122</v>
       </c>
       <c r="V28" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W28" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29">
+        <v>132</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29">
         <v>987991</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>5000000</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>18</v>
       </c>
-      <c r="H29">
-        <v>23</v>
-      </c>
       <c r="I29">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
-      <c r="K29" t="s">
-        <v>30</v>
+      <c r="K29">
+        <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M29" t="s">
         <v>39</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="s">
+        <v>40</v>
+      </c>
+      <c r="O29">
         <v>300000</v>
       </c>
-      <c r="U29" t="s">
-        <v>129</v>
-      </c>
       <c r="V29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="W29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30">
+        <v>136</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30">
         <v>987990</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>5000000</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>30</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>80</v>
-      </c>
-      <c r="I30">
-        <v>50</v>
       </c>
       <c r="J30">
         <v>50</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30">
+        <v>50</v>
+      </c>
+      <c r="L30" t="s">
+        <v>48</v>
+      </c>
+      <c r="P30" t="s">
+        <v>49</v>
+      </c>
+      <c r="R30">
+        <v>5000000</v>
+      </c>
+      <c r="T30" t="s">
+        <v>60</v>
+      </c>
+      <c r="U30">
+        <v>15000000</v>
+      </c>
+      <c r="V30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31">
+        <v>987990</v>
+      </c>
+      <c r="G31">
+        <v>5000000</v>
+      </c>
+      <c r="H31">
         <v>30</v>
       </c>
-      <c r="O30" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q30">
-        <v>5000000</v>
-      </c>
-      <c r="S30" t="s">
-        <v>58</v>
-      </c>
-      <c r="T30">
-        <v>15000000</v>
-      </c>
-      <c r="U30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31">
-        <v>987990</v>
-      </c>
-      <c r="F31">
-        <v>5000000</v>
-      </c>
-      <c r="G31">
-        <v>30</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>80</v>
-      </c>
-      <c r="I31">
-        <v>50</v>
       </c>
       <c r="J31">
         <v>50</v>
       </c>
-      <c r="K31" t="s">
-        <v>135</v>
-      </c>
-      <c r="O31" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q31">
+      <c r="K31">
+        <v>50</v>
+      </c>
+      <c r="L31" t="s">
+        <v>139</v>
+      </c>
+      <c r="P31" t="s">
+        <v>49</v>
+      </c>
+      <c r="R31">
         <v>5000000</v>
       </c>
-      <c r="S31" t="s">
-        <v>58</v>
-      </c>
-      <c r="T31">
+      <c r="T31" t="s">
+        <v>60</v>
+      </c>
+      <c r="U31">
         <v>15000000</v>
       </c>
-      <c r="U31" t="s">
-        <v>136</v>
-      </c>
       <c r="V31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="W31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32">
+        <v>143</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32">
         <v>987991</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>5000000</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>18</v>
       </c>
-      <c r="H32">
-        <v>23</v>
-      </c>
       <c r="I32">
+        <v>23</v>
+      </c>
+      <c r="J32">
         <v>5</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>1</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
+        <v>82</v>
+      </c>
+      <c r="V32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U32" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" t="s">
-        <v>142</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33">
+      <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33">
         <v>987992</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>10000000</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>60</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>85</v>
-      </c>
-      <c r="I33">
-        <v>25</v>
       </c>
       <c r="J33">
         <v>25</v>
       </c>
-      <c r="K33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K33">
+        <v>25</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="V33" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34">
+        <v>149</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34">
         <v>987991</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>5000000</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>18</v>
       </c>
-      <c r="H34">
-        <v>23</v>
-      </c>
       <c r="I34">
+        <v>23</v>
+      </c>
+      <c r="J34">
         <v>5</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>1</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
+        <v>82</v>
+      </c>
+      <c r="V34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35">
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35">
         <v>987992</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>10000000</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>60</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>85</v>
-      </c>
-      <c r="I35">
-        <v>25</v>
       </c>
       <c r="J35">
         <v>25</v>
       </c>
-      <c r="K35" t="s">
-        <v>30</v>
-      </c>
-      <c r="U35" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K35">
+        <v>25</v>
+      </c>
+      <c r="L35" t="s">
+        <v>32</v>
+      </c>
+      <c r="V35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36">
+        <v>155</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36">
         <v>987991</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>5000000</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>18</v>
       </c>
-      <c r="H36">
-        <v>23</v>
-      </c>
       <c r="I36">
+        <v>23</v>
+      </c>
+      <c r="J36">
         <v>5</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>1</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
+        <v>82</v>
+      </c>
+      <c r="V36" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" t="s">
-        <v>153</v>
-      </c>
-      <c r="C37" t="s">
-        <v>154</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37">
+      <c r="E37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37">
         <v>987992</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>5000000</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>60</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>85</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>81</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>67</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
+        <v>82</v>
+      </c>
+      <c r="V37" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U37" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" t="s">
-        <v>156</v>
-      </c>
-      <c r="C38" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38">
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38">
         <v>987991</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>5000000</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>18</v>
       </c>
-      <c r="H38">
-        <v>23</v>
-      </c>
       <c r="I38">
+        <v>23</v>
+      </c>
+      <c r="J38">
         <v>5</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>1</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
+        <v>82</v>
+      </c>
+      <c r="V38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U38" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>22</v>
-      </c>
-      <c r="B39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39">
+      <c r="E39" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39">
         <v>987992</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>5000000</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>60</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>85</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>81</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>67</v>
       </c>
-      <c r="K39" t="s">
-        <v>26</v>
-      </c>
-      <c r="U39" t="s">
-        <v>161</v>
+      <c r="L39" t="s">
+        <v>82</v>
+      </c>
+      <c r="V39" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3060,387 +3202,387 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>165</v>
+      <c r="A1" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>169</v>
+      <c r="A2" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>169</v>
+      <c r="B3" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="C21" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="C22" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="C23" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="18" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="5"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>208</v>
+      <c r="A29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>211</v>
+      <c r="B30" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3461,131 +3603,131 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>213</v>
+      <c r="A1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="2" ht="33.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>215</v>
+      <c r="A2" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="3" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>217</v>
+      <c r="A3" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="4" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>219</v>
+      <c r="A4" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="5" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>221</v>
+      <c r="A5" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="6" ht="33.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>223</v>
+      <c r="A6" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="7" ht="68.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>225</v>
+      <c r="A7" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="8" ht="33.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>227</v>
+      <c r="A8" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="9" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>229</v>
+      <c r="A9" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B13" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B14" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B15" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3607,13 +3749,13 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3624,7 +3766,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3635,7 +3777,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -3646,7 +3788,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3657,7 +3799,7 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3668,7 +3810,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3679,7 +3821,7 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3690,7 +3832,7 @@
         <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3701,12 +3843,12 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3729,178 +3871,178 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" t="s">
         <v>254</v>
       </c>
-      <c r="B4" t="s">
-        <v>250</v>
-      </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B11" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C13" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B16" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
